--- a/artfynd/A 32938-2025 artfynd.xlsx
+++ b/artfynd/A 32938-2025 artfynd.xlsx
@@ -981,37 +981,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126358548</v>
+        <v>126359370</v>
       </c>
       <c r="B5" t="n">
-        <v>98352</v>
+        <v>57656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1020,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597807</v>
+        <v>597720</v>
       </c>
       <c r="R5" t="n">
-        <v>6925924</v>
+        <v>6926153</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1189,38 +1195,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126359370</v>
+        <v>126358548</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1229,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597720</v>
+        <v>597807</v>
       </c>
       <c r="R7" t="n">
-        <v>6926153</v>
+        <v>6925924</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,11 +1270,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126357715</v>
+        <v>126359594</v>
       </c>
       <c r="B10" t="n">
-        <v>91262</v>
+        <v>57656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,34 +1511,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597769</v>
+        <v>597756</v>
       </c>
       <c r="R10" t="n">
-        <v>6925979</v>
+        <v>6926156</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,6 +1576,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Årsfärska spår.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1597,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126359594</v>
+        <v>126357715</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>91262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,39 +1618,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597756</v>
+        <v>597769</v>
       </c>
       <c r="R11" t="n">
-        <v>6926156</v>
+        <v>6925979</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,11 +1678,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Årsfärska spår.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 32938-2025 artfynd.xlsx
+++ b/artfynd/A 32938-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126358426</v>
+        <v>126357685</v>
       </c>
       <c r="B2" t="n">
-        <v>57653</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597819</v>
+        <v>597779</v>
       </c>
       <c r="R2" t="n">
-        <v>6925931</v>
+        <v>6925954</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126357685</v>
+        <v>126358426</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>57653</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597779</v>
+        <v>597819</v>
       </c>
       <c r="R3" t="n">
-        <v>6925954</v>
+        <v>6925931</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -981,38 +981,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126359370</v>
+        <v>126358548</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1021,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597720</v>
+        <v>597807</v>
       </c>
       <c r="R5" t="n">
-        <v>6926153</v>
+        <v>6925924</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1056,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1082,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126357848</v>
+        <v>126359370</v>
       </c>
       <c r="B6" t="n">
         <v>57656</v>
@@ -1128,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597769</v>
+        <v>597720</v>
       </c>
       <c r="R6" t="n">
-        <v>6925979</v>
+        <v>6926153</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,37 +1189,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126358548</v>
+        <v>126357848</v>
       </c>
       <c r="B7" t="n">
-        <v>98352</v>
+        <v>57656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1234,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597807</v>
+        <v>597769</v>
       </c>
       <c r="R7" t="n">
-        <v>6925924</v>
+        <v>6925979</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,6 +1265,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 32938-2025 artfynd.xlsx
+++ b/artfynd/A 32938-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126357685</v>
+        <v>126358426</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597779</v>
+        <v>597819</v>
       </c>
       <c r="R2" t="n">
-        <v>6925954</v>
+        <v>6925931</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126358426</v>
+        <v>126357685</v>
       </c>
       <c r="B3" t="n">
-        <v>57653</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,16 +788,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597819</v>
+        <v>597779</v>
       </c>
       <c r="R3" t="n">
-        <v>6925931</v>
+        <v>6925954</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126359594</v>
+        <v>126357715</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>91262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,39 +1511,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597756</v>
+        <v>597769</v>
       </c>
       <c r="R10" t="n">
-        <v>6926156</v>
+        <v>6925979</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,11 +1571,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Årsfärska spår.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126357715</v>
+        <v>126359594</v>
       </c>
       <c r="B11" t="n">
-        <v>91262</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1618,34 +1608,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597769</v>
+        <v>597756</v>
       </c>
       <c r="R11" t="n">
-        <v>6925979</v>
+        <v>6926156</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,6 +1673,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Årsfärska spår.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 32938-2025 artfynd.xlsx
+++ b/artfynd/A 32938-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126358426</v>
+        <v>126357685</v>
       </c>
       <c r="B2" t="n">
-        <v>57653</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597819</v>
+        <v>597779</v>
       </c>
       <c r="R2" t="n">
-        <v>6925931</v>
+        <v>6925954</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126357685</v>
+        <v>126358426</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>57654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597779</v>
+        <v>597819</v>
       </c>
       <c r="R3" t="n">
-        <v>6925954</v>
+        <v>6925931</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +887,7 @@
         <v>126358217</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,37 +981,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126358548</v>
+        <v>126357848</v>
       </c>
       <c r="B5" t="n">
-        <v>98352</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1020,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597807</v>
+        <v>597769</v>
       </c>
       <c r="R5" t="n">
-        <v>6925924</v>
+        <v>6925979</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,7 +1091,7 @@
         <v>126359370</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,38 +1195,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126357848</v>
+        <v>126358548</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>98361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1229,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597769</v>
+        <v>597807</v>
       </c>
       <c r="R7" t="n">
-        <v>6925979</v>
+        <v>6925924</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,11 +1270,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,7 +1299,7 @@
         <v>126359891</v>
       </c>
       <c r="B8" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>126359564</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126357715</v>
+        <v>126359594</v>
       </c>
       <c r="B10" t="n">
-        <v>91262</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,34 +1511,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597769</v>
+        <v>597756</v>
       </c>
       <c r="R10" t="n">
-        <v>6925979</v>
+        <v>6926156</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,6 +1576,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Årsfärska spår.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1597,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126359594</v>
+        <v>126357715</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>91265</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,39 +1618,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597756</v>
+        <v>597769</v>
       </c>
       <c r="R11" t="n">
-        <v>6926156</v>
+        <v>6925979</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,11 +1678,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Årsfärska spår.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1707,7 +1707,7 @@
         <v>126359428</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>126358139</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>126359013</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 32938-2025 artfynd.xlsx
+++ b/artfynd/A 32938-2025 artfynd.xlsx
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126357848</v>
+        <v>126359370</v>
       </c>
       <c r="B5" t="n">
         <v>57657</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597769</v>
+        <v>597720</v>
       </c>
       <c r="R5" t="n">
-        <v>6925979</v>
+        <v>6926153</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126359370</v>
+        <v>126357848</v>
       </c>
       <c r="B6" t="n">
         <v>57657</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597720</v>
+        <v>597769</v>
       </c>
       <c r="R6" t="n">
-        <v>6926153</v>
+        <v>6925979</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126359594</v>
+        <v>126357715</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>91265</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,39 +1511,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597756</v>
+        <v>597769</v>
       </c>
       <c r="R10" t="n">
-        <v>6926156</v>
+        <v>6925979</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,11 +1571,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Årsfärska spår.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126357715</v>
+        <v>126359594</v>
       </c>
       <c r="B11" t="n">
-        <v>91265</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1618,34 +1608,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597769</v>
+        <v>597756</v>
       </c>
       <c r="R11" t="n">
-        <v>6925979</v>
+        <v>6926156</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,6 +1673,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Årsfärska spår.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 32938-2025 artfynd.xlsx
+++ b/artfynd/A 32938-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126357685</v>
+        <v>126358426</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597779</v>
+        <v>597819</v>
       </c>
       <c r="R2" t="n">
-        <v>6925954</v>
+        <v>6925931</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126358426</v>
+        <v>126357685</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,16 +788,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597819</v>
+        <v>597779</v>
       </c>
       <c r="R3" t="n">
-        <v>6925931</v>
+        <v>6925954</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 32938-2025 artfynd.xlsx
+++ b/artfynd/A 32938-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126358426</v>
+        <v>126357685</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597819</v>
+        <v>597779</v>
       </c>
       <c r="R2" t="n">
-        <v>6925931</v>
+        <v>6925954</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126357685</v>
+        <v>126358426</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597779</v>
+        <v>597819</v>
       </c>
       <c r="R3" t="n">
-        <v>6925954</v>
+        <v>6925931</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 32938-2025 artfynd.xlsx
+++ b/artfynd/A 32938-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>126358426</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32938-2025 artfynd.xlsx
+++ b/artfynd/A 32938-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>126358426</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32938-2025 artfynd.xlsx
+++ b/artfynd/A 32938-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>126358426</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32938-2025 artfynd.xlsx
+++ b/artfynd/A 32938-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>126358426</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32938-2025 artfynd.xlsx
+++ b/artfynd/A 32938-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>126358426</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32938-2025 artfynd.xlsx
+++ b/artfynd/A 32938-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>126358426</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32938-2025 artfynd.xlsx
+++ b/artfynd/A 32938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126357685</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>126359370</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>126357848</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>126359564</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>126359594</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>126359428</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>126358139</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>126359013</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 32938-2025 artfynd.xlsx
+++ b/artfynd/A 32938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126357685</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>126359370</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>126357848</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>126359564</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>126359594</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>126359428</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>126358139</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>126359013</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 32938-2025 artfynd.xlsx
+++ b/artfynd/A 32938-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126357685</v>
+        <v>126357715</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597779</v>
+        <v>597769</v>
       </c>
       <c r="R2" t="n">
-        <v>6925954</v>
+        <v>6925979</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126358426</v>
+        <v>126358217</v>
       </c>
       <c r="B3" t="n">
-        <v>57681</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597819</v>
+        <v>597838</v>
       </c>
       <c r="R3" t="n">
-        <v>6925931</v>
+        <v>6925930</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,45 +869,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126358217</v>
+        <v>126358426</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597838</v>
+        <v>597819</v>
       </c>
       <c r="R4" t="n">
-        <v>6925930</v>
+        <v>6925931</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126359370</v>
+        <v>126357685</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,7 +1002,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1021,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597720</v>
+        <v>597779</v>
       </c>
       <c r="R5" t="n">
-        <v>6926153</v>
+        <v>6925954</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1081,7 @@
         <v>126357848</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,37 +1185,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126358548</v>
+        <v>126358139</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1234,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597807</v>
+        <v>597821</v>
       </c>
       <c r="R7" t="n">
-        <v>6925924</v>
+        <v>6925945</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,45 +1292,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126359891</v>
+        <v>126359013</v>
       </c>
       <c r="B8" t="n">
-        <v>97239</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597813</v>
+        <v>597795</v>
       </c>
       <c r="R8" t="n">
-        <v>6926065</v>
+        <v>6926064</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,6 +1368,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126359564</v>
+        <v>126359370</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1424,7 +1430,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1433,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597725</v>
+        <v>597720</v>
       </c>
       <c r="R9" t="n">
-        <v>6926163</v>
+        <v>6926153</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126357715</v>
+        <v>126359428</v>
       </c>
       <c r="B10" t="n">
-        <v>91265</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,34 +1517,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597769</v>
+        <v>597702</v>
       </c>
       <c r="R10" t="n">
-        <v>6925979</v>
+        <v>6926159</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,6 +1582,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1597,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126359594</v>
+        <v>126359564</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597756</v>
+        <v>597725</v>
       </c>
       <c r="R11" t="n">
-        <v>6926156</v>
+        <v>6926163</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,7 +1693,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall.  Årsfärska spår.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1704,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126359428</v>
+        <v>126359594</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1744,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597702</v>
+        <v>597756</v>
       </c>
       <c r="R12" t="n">
-        <v>6926159</v>
+        <v>6926156</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1784,7 +1800,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.  Årsfärska spår.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1811,38 +1827,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126358139</v>
+        <v>126358548</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1851,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597821</v>
+        <v>597807</v>
       </c>
       <c r="R13" t="n">
-        <v>6925945</v>
+        <v>6925924</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,11 +1902,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1918,50 +1928,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126359013</v>
+        <v>126359891</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>97983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597795</v>
+        <v>597813</v>
       </c>
       <c r="R14" t="n">
-        <v>6926064</v>
+        <v>6926065</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,11 +1999,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 32938-2025 artfynd.xlsx
+++ b/artfynd/A 32938-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126357715</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126358217</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126358426</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126357685</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126357848</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126358139</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126359013</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1503,6 +1543,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126359370</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1610,6 +1655,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126359428</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126359564</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1824,6 +1879,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126359594</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1925,6 +1985,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126358548</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2022,8 +2087,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126359891</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>